--- a/DataTables/DetailText/剧情/010知州有请.xlsx
+++ b/DataTables/DetailText/剧情/010知州有请.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0173E941-D3B4-4244-A83E-52D67E32826A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C85FD52-55D0-4EE4-B8E4-E20D6A179A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>StoryID</t>
   </si>
@@ -213,6 +213,355 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>杨善泉</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>位到我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>画押，排好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>队</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一个一个来，写好收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>地址，我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>专</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>门派人运送。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李言闻</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>几日我去菜市街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>菜得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>候，看到不少流民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在城东，大灾之后必有大疫，朝廷这次赈灾太及时了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮，跟我去后院收拾收拾库房，一会儿药材就要送来了，得赶紧腾出地方。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>知州有请</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>009_01</t>
+  </si>
+  <si>
+    <r>
+      <t>好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嘞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/010/010_01.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/010/010_02.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>一会儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>位就去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>库</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>房画押</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>登记</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，明日起官府会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发放榜文通知百姓就近领取药材。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <t>浙江省淳安建德两</t>
     </r>
@@ -234,13 +583,23 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>突发水灾，周边各地已有瘟疫出现，朝廷为防止疫情扩散，特调拨赈灾药材发放沿途州府。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>昨日</t>
+      <t>突发水灾，周边各地已有瘟疫出现，朝廷为防止疫情扩散，特令周边州府发放赈灾药材。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>昨日衙门</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采购的</t>
     </r>
     <r>
       <rPr>
@@ -390,6 +749,176 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
+      <t>诊治发放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>好的好的。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>朝廷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调拨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>灾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>材，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>次不光惠民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>局，咱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>些医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>馆药铺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>也要一起帮忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
       <t>发</t>
     </r>
     <r>
@@ -400,667 +929,35 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药材。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>一会儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>位就去</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>库</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>房画押取</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，明日起官府会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发放榜文通知百姓就近领取药材。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>杨善泉</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>诸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>位到我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>画押，排好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>队</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一个一个来，写好收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>地址，我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>专</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>门派人运送。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李东璧</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>可是还没辨验药材就直接装车了吗？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>箱子上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>都贴着封条，都是太医院直接调拨过来的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>难道你还信不过朝廷吗？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>快画押吧李大夫，上面催得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>紧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>赶着出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>呢。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李言闻</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>东璧啊回来了啦，什么事儿啊一大早就被叫去了？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>朝廷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>调拨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>灾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>材，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>次不光惠民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>局，咱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>些医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>馆药铺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>也要一起帮忙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>材。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>吴芷兰</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>几日我去菜市街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>菜得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>候，看到不少流民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在城东，大灾之后必有大疫，朝廷这次赈灾太及时了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮，跟我去后院收拾收拾库房，一会儿药材就要送来了，得赶紧腾出地方。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>010</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>知州有请</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>009_01</t>
-  </si>
-  <si>
-    <r>
-      <t>好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>嘞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/010/010_01.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/010/010_02.png</t>
+      <t>放。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧回来了啦，什么事儿啊一大早就被叫去了？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李大夫您在这画押，上面催得紧，我们赶着出货呢。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1194,7 +1091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1245,6 +1142,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1600,10 +1500,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -1619,7 +1519,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="17" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1703,7 +1603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1758,7 +1658,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>29</v>
@@ -1782,7 +1682,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1805,7 +1705,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>36</v>
@@ -1828,7 +1728,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1848,7 +1748,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1866,11 +1766,11 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1881,18 +1781,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1903,16 +1803,18 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>45</v>
+      <c r="H9" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1923,93 +1825,91 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>47</v>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="8" t="s">
-        <v>41</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>50</v>
+      <c r="G13" s="3"/>
+      <c r="H13" s="19" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -2018,68 +1918,48 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="19" t="s">
-        <v>53</v>
+      <c r="H15" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
@@ -2111,26 +1991,6 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/010知州有请.xlsx
+++ b/DataTables/DetailText/剧情/010知州有请.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C85FD52-55D0-4EE4-B8E4-E20D6A179A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19467384-A986-4223-981D-A5C2BEC27F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,18 +588,32 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>昨日衙门</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>采购的</t>
+    <t>好的好的。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>朝廷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调拨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了</t>
     </r>
     <r>
       <rPr>
@@ -639,27 +653,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>材已到了咱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们蕲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>州，</t>
+      <t>材，</t>
     </r>
     <r>
       <rPr>
@@ -679,6 +673,199 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>次不光惠民</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>局，咱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>些医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>馆药铺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>也要一起帮忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>放。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>璧回来了啦，什么事儿啊一大早就被叫去了？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李大夫您在这画押，上面催得紧，我们赶着出货呢。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>昨日，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>灾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>材已</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采办完备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>次除了惠民</t>
     </r>
     <r>
@@ -761,203 +948,6 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>好的好的。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>朝廷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>调拨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>灾</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>材，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>次不光惠民</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>局，咱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>些医</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>馆药铺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>也要一起帮忙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>放。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>璧回来了啦，什么事儿啊一大早就被叫去了？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>李大夫您在这画押，上面催得紧，我们赶着出货呢。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1748,7 +1738,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1814,7 +1804,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1836,7 +1826,7 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1858,7 +1848,7 @@
         <v>29</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1878,7 +1868,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
